--- a/data/trans_orig/IP31KM14_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM14_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16059</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10509</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22644</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10838</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5841</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17311</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27555</t>
+          <t>27841</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37656</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31071</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43206</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>42861</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36388</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47858</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>79,82%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>34123</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34619</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47411</t>
+          <t>38935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>84488</t>
+          <t>71779</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>79539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>79751</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>65163</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>96926</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>80872</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62975</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>97666</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,94%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91195</t>
+          <t>78183</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74921</t>
+          <t>64826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112264</t>
+          <t>93290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172067</t>
+          <t>157934</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>146295</t>
+          <t>139412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197372</t>
+          <t>180166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>386672</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>369497</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>401260</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>512</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>370960</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>354166</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>388857</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>414055</t>
+          <t>346483</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392986</t>
+          <t>331376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430329</t>
+          <t>359840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>785015</t>
+          <t>733156</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>759710</t>
+          <t>710924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810787</t>
+          <t>751678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32045</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23970</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42481</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21053</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14952</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29711</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33298</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25068</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54351</t>
+          <t>53778</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42873</t>
+          <t>42191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>67157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>125133</t>
+          <t>134641</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116475</t>
+          <t>124205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131234</t>
+          <t>142716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>147841</t>
+          <t>125406</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136933</t>
+          <t>116740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156071</t>
+          <t>132607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>272973</t>
+          <t>260047</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259309</t>
+          <t>246668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284451</t>
+          <t>271634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>127855</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>110698</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>148862</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>112763</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>93912</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>131731</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>111698</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120956</t>
+          <t>96513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168997</t>
+          <t>128583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>253973</t>
+          <t>239553</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225952</t>
+          <t>215569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>285042</t>
+          <t>265274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>558969</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>537962</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>576126</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>758</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>538954</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>519986</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>557805</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>603523</t>
+          <t>506013</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575736</t>
+          <t>489128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623777</t>
+          <t>521198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1142477</t>
+          <t>1064982</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1111408</t>
+          <t>1039261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1170498</t>
+          <t>1088966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
